--- a/docs/downloads/23082026Tduh Developer Project Sales Status 13.xlsx
+++ b/docs/downloads/23082026Tduh Developer Project Sales Status 13.xlsx
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>ARTE STAR 
+          <t>ARTE STAR
 MILANO</t>
         </is>
       </c>
